--- a/Lista de clientes MBR.xlsx
+++ b/Lista de clientes MBR.xlsx
@@ -14,7 +14,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$288</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4135,7 +4134,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
